--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 13:26</t>
+          <t>更新时间: 2026-09-14 13:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 13:31</t>
+          <t>更新时间: 2026-09-15 13:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 13:30</t>
+          <t>更新时间: 2026-09-16 13:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 13:23</t>
+          <t>更新时间: 2026-09-17 13:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 13:32</t>
+          <t>更新时间: 2026-09-18 13:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 13:20</t>
+          <t>更新时间: 2026-09-19 13:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 13:12</t>
+          <t>更新时间: 2026-09-20 13:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 13:30</t>
+          <t>更新时间: 2026-09-21 13:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 13:34</t>
+          <t>更新时间: 2026-09-22 13:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 13:31</t>
+          <t>更新时间: 2026-09-23 13:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 13:18</t>
+          <t>更新时间: 2026-09-24 13:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 13:33</t>
+          <t>更新时间: 2026-09-25 13:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 13:32</t>
+          <t>更新时间: 2026-09-26 13:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 13:38</t>
+          <t>更新时间: 2026-09-27 13:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 13:54</t>
+          <t>更新时间: 2026-09-28 14:00</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 14:00</t>
+          <t>更新时间: 2026-09-29 14:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 14:19</t>
+          <t>更新时间: 2026-09-30 14:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 14:05</t>
+          <t>更新时间: 2026-10-01 14:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 14:38</t>
+          <t>更新时间: 2026-10-02 14:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 14:23</t>
+          <t>更新时间: 2026-10-03 13:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 13:51</t>
+          <t>更新时间: 2026-10-04 14:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 14:28</t>
+          <t>更新时间: 2026-10-05 14:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 14:20</t>
+          <t>更新时间: 2026-10-06 14:56</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 14:56</t>
+          <t>更新时间: 2026-10-07 14:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 14:37</t>
+          <t>更新时间: 2026-10-08 14:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 14:44</t>
+          <t>更新时间: 2026-10-09 14:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 14:52</t>
+          <t>更新时间: 2026-10-10 14:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 14:28</t>
+          <t>更新时间: 2026-10-11 14:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 14:34</t>
+          <t>更新时间: 2026-10-12 14:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 14:39</t>
+          <t>更新时间: 2026-10-13 15:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 15:10</t>
+          <t>更新时间: 2026-10-14 13:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 13:32</t>
+          <t>更新时间: 2026-10-15 13:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-15 13:21</t>
+          <t>更新时间: 2026-10-16 13:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-16 13:12</t>
+          <t>更新时间: 2026-10-17 13:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-17 13:06</t>
+          <t>更新时间: 2026-10-18 13:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-18 13:13</t>
+          <t>更新时间: 2026-10-19 13:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-19 13:25</t>
+          <t>更新时间: 2026-10-20 13:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-20 13:27</t>
+          <t>更新时间: 2026-10-21 13:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-21 13:25</t>
+          <t>更新时间: 2026-10-22 13:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-22 13:31</t>
+          <t>更新时间: 2026-10-23 13:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-23 13:31</t>
+          <t>更新时间: 2026-10-24 13:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-24 13:08</t>
+          <t>更新时间: 2026-10-25 13:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-25 13:24</t>
+          <t>更新时间: 2026-10-26 13:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-26 13:29</t>
+          <t>更新时间: 2026-10-27 13:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-27 13:45</t>
+          <t>更新时间: 2026-10-28 14:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-28 14:24</t>
+          <t>更新时间: 2026-10-29 14:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-29 14:34</t>
+          <t>更新时间: 2026-10-30 14:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-30 14:33</t>
+          <t>更新时间: 2026-10-31 14:23</t>
         </is>
       </c>
     </row>
